--- a/artfynd/A 57294-2024 artfynd.xlsx
+++ b/artfynd/A 57294-2024 artfynd.xlsx
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -894,7 +894,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -1016,7 +1016,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>

--- a/artfynd/A 57294-2024 artfynd.xlsx
+++ b/artfynd/A 57294-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>62430991</v>
       </c>
       <c r="B2" t="n">
-        <v>99121</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101947</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501061.7367123128</v>
+        <v>501062</v>
       </c>
       <c r="R2" t="n">
-        <v>6537098.072230474</v>
+        <v>6537098</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1982-05-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1982-05-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62431004</v>
+        <v>62430995</v>
       </c>
       <c r="B3" t="n">
-        <v>99121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501160.8740048479</v>
+        <v>501161</v>
       </c>
       <c r="R3" t="n">
-        <v>6537199.668164865</v>
+        <v>6537200</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -867,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1988-05-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-06-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1988-05-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-06-20</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -901,7 +871,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Skogshage med urkalkhällar</t>
+          <t>Kalkberg</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -922,12 +892,7 @@
         <v>62430996</v>
       </c>
       <c r="B4" t="n">
-        <v>99121</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501159.2945383618</v>
+        <v>501159</v>
       </c>
       <c r="R4" t="n">
-        <v>6537299.17009158</v>
+        <v>6537299</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -992,19 +957,9 @@
           <t>1988-05-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1988-05-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1041,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>57194982</v>
+        <v>57769222</v>
       </c>
       <c r="B5" t="n">
-        <v>96926</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222295</v>
+        <v>220103</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>(L.) Walther</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501160.8740048479</v>
+        <v>501161</v>
       </c>
       <c r="R5" t="n">
-        <v>6537199.668164865</v>
+        <v>6537200</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1111,22 +1061,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1988-05-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-06-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1988-05-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-06-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2 fläckar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,7 +1085,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Skogshage med urkalkhällar</t>
+          <t>Kalkberg</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1158,15 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>57194973</v>
+        <v>57769229</v>
       </c>
       <c r="B6" t="n">
-        <v>96926</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108194</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,34 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222295</v>
+        <v>220103</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>(L.) Walther</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ödeskärr 9350/4750, Nrk</t>
+          <t>Örberga 9550/4850, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>501061.7367123128</v>
+        <v>501159</v>
       </c>
       <c r="R6" t="n">
-        <v>6537098.072230474</v>
+        <v>6537299</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1228,22 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1982-05-31</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1982-05-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1982-05-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1982-05-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,7 +1187,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Urkalkhäll N-ut från skogshörnet</t>
+          <t>Välbetad ängsmark vid åkerväg bland gamla brott</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1275,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>57197825</v>
+        <v>62086003</v>
       </c>
       <c r="B7" t="n">
-        <v>96953</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222309</v>
+        <v>220204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1315,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>501160.8740048479</v>
+        <v>501161</v>
       </c>
       <c r="R7" t="n">
-        <v>6537199.668164865</v>
+        <v>6537200</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1348,19 +1273,9 @@
           <t>1982-05-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1982-05-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,15 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>57769222</v>
+        <v>62431694</v>
       </c>
       <c r="B8" t="n">
-        <v>105123</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220103</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1432,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>501160.8740048479</v>
+        <v>501161</v>
       </c>
       <c r="R8" t="n">
-        <v>6537199.668164865</v>
+        <v>6537200</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1462,27 +1372,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1995-06-20</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1988-05-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1995-06-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2 fläckar</t>
+          <t>1988-05-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,7 +1391,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkberg</t>
+          <t>Skogshage med urkalkhällar</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1514,50 +1409,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>57769229</v>
+        <v>62362046</v>
       </c>
       <c r="B9" t="n">
-        <v>105123</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220103</v>
+        <v>221141</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Örberga 9550/4850, Nrk</t>
+          <t>Örberga 9450/4850, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>501159.2945383618</v>
+        <v>501161</v>
       </c>
       <c r="R9" t="n">
-        <v>6537299.17009158</v>
+        <v>6537200</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1584,22 +1474,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1982-05-29</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-06-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1982-05-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-06-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,7 +1493,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Välbetad ängsmark vid åkerväg bland gamla brott</t>
+          <t>Kalkberg</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1631,15 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>62082652</v>
+        <v>62362048</v>
       </c>
       <c r="B10" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,34 +1522,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Örberga 9450/4850, Nrk</t>
+          <t>Örberga 9550/4850, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>501160.8740048479</v>
+        <v>501159</v>
       </c>
       <c r="R10" t="n">
-        <v>6537199.668164865</v>
+        <v>6537299</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1704,21 +1579,11 @@
           <t>1988-05-28</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>1988-05-28</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1730,7 +1595,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Skogshage med urkalkhällar</t>
+          <t>Kalkbrott i skogshage</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1748,15 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>62082628</v>
+        <v>62531185</v>
       </c>
       <c r="B11" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,37 +1624,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>222002</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Örberga 9450/4550, Nrk</t>
+          <t>Örberga 9450/4850, Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500905.7305668122</v>
+        <v>501161</v>
       </c>
       <c r="R11" t="n">
-        <v>6537196.506203163</v>
+        <v>6537200</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1818,27 +1678,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2015-06-04</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1988-05-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2015-06-04</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Riklig</t>
+          <t>1988-05-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1849,6 +1694,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Skogshage med urkalkhällar</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1865,15 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>62086003</v>
+        <v>62536644</v>
       </c>
       <c r="B12" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103691</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1881,34 +1726,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220204</v>
+        <v>222009</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Viola rupestris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Örberga 9450/4850, Nrk</t>
+          <t>Ödeskärr 9350/4750, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>501160.8740048479</v>
+        <v>501062</v>
       </c>
       <c r="R12" t="n">
-        <v>6537199.668164865</v>
+        <v>6537098</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1935,22 +1784,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>1982-05-29</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1982-05-31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1982-05-29</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1982-05-31</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Åtminstone 19 ex inom 3x5 m</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1964,7 +1808,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Välbetad ängsmark vid åkerväg bland gamla brott</t>
+          <t>Urkalkhäll N-ut från skogshörnet</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1982,53 +1826,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>62082632</v>
+        <v>62304840</v>
       </c>
       <c r="B13" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102560</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>222133</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Örberga 9550/4850, Nrk</t>
+          <t>Örberga 9450/4650, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501159.2945383618</v>
+        <v>501005</v>
       </c>
       <c r="R13" t="n">
-        <v>6537299.17009158</v>
+        <v>6537242</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2052,22 +1891,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>1960-01-01</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1960-12-31</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2078,11 +1907,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Kalkberg 12</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2099,32 +1923,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>62362058</v>
+        <v>62304856</v>
       </c>
       <c r="B14" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102560</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221141</v>
+        <v>222133</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2139,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501160.8740048479</v>
+        <v>501161</v>
       </c>
       <c r="R14" t="n">
-        <v>6537199.668164865</v>
+        <v>6537200</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2172,24 +1991,9 @@
           <t>1988-05-28</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>1988-05-28</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Riklig</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2221,50 +2025,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>62362048</v>
+        <v>57194973</v>
       </c>
       <c r="B15" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99754</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221141</v>
+        <v>222295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Örberga 9550/4850, Nrk</t>
+          <t>Ödeskärr 9350/4750, Nrk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>501159.2945383618</v>
+        <v>501062</v>
       </c>
       <c r="R15" t="n">
-        <v>6537299.17009158</v>
+        <v>6537098</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2291,22 +2090,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>1988-05-28</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1982-05-31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1988-05-28</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1982-05-31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2320,7 +2109,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkbrott i skogshage</t>
+          <t>Urkalkhäll N-ut från skogshörnet</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2338,15 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>62431694</v>
+        <v>57194982</v>
       </c>
       <c r="B16" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99754</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,21 +2138,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220299</v>
+        <v>222295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2378,10 +2162,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>501160.8740048479</v>
+        <v>501161</v>
       </c>
       <c r="R16" t="n">
-        <v>6537199.668164865</v>
+        <v>6537200</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2411,19 +2195,9 @@
           <t>1988-05-28</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>1988-05-28</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2455,37 +2229,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>62531185</v>
+        <v>57197825</v>
       </c>
       <c r="B17" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99781</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222002</v>
+        <v>222309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Backstarr</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Carex ericetorum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2495,10 +2264,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>501160.8740048479</v>
+        <v>501161</v>
       </c>
       <c r="R17" t="n">
-        <v>6537199.668164865</v>
+        <v>6537200</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2525,22 +2294,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>1988-05-28</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1982-05-29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1988-05-28</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1982-05-29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2554,7 +2313,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Skogshage med urkalkhällar</t>
+          <t>Välbetad ängsmark vid åkerväg bland gamla brott</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2572,57 +2331,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>62536644</v>
+        <v>62082628</v>
       </c>
       <c r="B18" t="n">
-        <v>101128</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222009</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Viola rupestris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>F. W. Schmidt</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ödeskärr 9350/4750, Nrk</t>
+          <t>Örberga 9450/4550, Nrk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>501061.7367123128</v>
+        <v>500906</v>
       </c>
       <c r="R18" t="n">
-        <v>6537098.072230474</v>
+        <v>6537197</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2646,27 +2396,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>1982-05-31</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1982-05-31</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-04</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Åtminstone 19 ex inom 3x5 m</t>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2677,11 +2417,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Urkalkhäll N-ut från skogshörnet</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2698,54 +2433,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>62891803</v>
+        <v>62082629</v>
       </c>
       <c r="B19" t="n">
-        <v>98537</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222886</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Örberga 9450/4850, Nrk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>501160.8740048479</v>
+        <v>501161</v>
       </c>
       <c r="R19" t="n">
-        <v>6537199.668164865</v>
+        <v>6537200</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2772,27 +2498,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>1988-05-28</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-06-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1988-05-28</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>1 ex med 6 fröställningar</t>
+          <t>1995-06-20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2806,7 +2517,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Skogshage med urkalkhällar</t>
+          <t>Kalkberg</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2821,6 +2532,219 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>62082632</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Örberga 9550/4850, Nrk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>501159</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6537299</v>
+      </c>
+      <c r="S20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1960-12-31</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Kalkberg 12</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>62891803</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101346</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222886</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Backsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pulsatilla vulgaris</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Örberga 9450/4850, Nrk</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>501161</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6537200</v>
+      </c>
+      <c r="S21" t="n">
+        <v>50</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>1988-05-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>1988-05-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>1 ex med 6 fröställningar</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Skogshage med urkalkhällar</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57294-2024 artfynd.xlsx
+++ b/artfynd/A 57294-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62430991</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62430995</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62430996</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57769222</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57769229</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62086003</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1406,6 +1441,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62431694</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62362046</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1610,6 +1655,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62362048</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1712,6 +1762,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62531185</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1823,6 +1878,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62536644</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1920,6 +1980,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62304840</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2022,6 +2087,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62304856</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2124,6 +2194,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57194973</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2226,6 +2301,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57194982</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2328,6 +2408,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57197825</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2430,6 +2515,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62082628</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2532,6 +2622,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62082629</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2634,6 +2729,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62082632</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2745,8 +2845,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62891803</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>